--- a/data/raw/german_credit_processed.xlsx
+++ b/data/raw/german_credit_processed.xlsx
@@ -667,7 +667,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -833,7 +833,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -7077,7 +7077,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -7927,7 +7927,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -9159,7 +9159,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F167" t="n">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -9885,7 +9885,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -10333,7 +10333,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -10615,7 +10615,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -10727,7 +10727,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F191" t="n">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F192" t="n">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F193" t="n">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F194" t="n">
@@ -11519,7 +11519,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F199" t="n">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -12025,7 +12025,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F208" t="n">
@@ -12079,7 +12079,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F209" t="n">
@@ -12137,7 +12137,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F210" t="n">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F214" t="n">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F215" t="n">
@@ -12569,7 +12569,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F218" t="n">
@@ -12685,7 +12685,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F220" t="n">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F225" t="n">
@@ -13067,7 +13067,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F227" t="n">
@@ -13179,7 +13179,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F229" t="n">
@@ -13291,7 +13291,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F231" t="n">
@@ -13739,7 +13739,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F239" t="n">
@@ -14075,7 +14075,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F245" t="n">
@@ -14183,7 +14183,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -14345,7 +14345,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F250" t="n">
@@ -14515,7 +14515,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F253" t="n">
@@ -14631,7 +14631,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F255" t="n">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F256" t="n">
@@ -15013,7 +15013,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F262" t="n">
@@ -15353,7 +15353,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F268" t="n">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -15781,7 +15781,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F276" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -16001,7 +16001,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -16271,7 +16271,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F285" t="n">
@@ -16669,7 +16669,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F292" t="n">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F296" t="n">
@@ -16947,7 +16947,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F297" t="n">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F300" t="n">
@@ -17159,7 +17159,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F301" t="n">
@@ -17495,7 +17495,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F307" t="n">
@@ -17657,7 +17657,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -17827,7 +17827,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F313" t="n">
@@ -17881,7 +17881,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -18051,7 +18051,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -18109,7 +18109,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -18167,7 +18167,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -18275,7 +18275,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F321" t="n">
@@ -18507,7 +18507,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F325" t="n">
@@ -18677,7 +18677,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -19121,7 +19121,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F336" t="n">
@@ -19179,7 +19179,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F337" t="n">
@@ -19295,7 +19295,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F339" t="n">
@@ -19349,7 +19349,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F340" t="n">
@@ -19407,7 +19407,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -19523,7 +19523,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F343" t="n">
@@ -19639,7 +19639,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -19925,7 +19925,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F350" t="n">
@@ -20037,7 +20037,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F352" t="n">
@@ -20091,7 +20091,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F353" t="n">
@@ -20527,7 +20527,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F361" t="n">
@@ -20751,7 +20751,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F365" t="n">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F366" t="n">
@@ -20863,7 +20863,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F367" t="n">
@@ -20971,7 +20971,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F369" t="n">
@@ -21029,7 +21029,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F370" t="n">
@@ -21087,7 +21087,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F371" t="n">
@@ -21249,7 +21249,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F374" t="n">
@@ -21411,7 +21411,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F377" t="n">
@@ -21685,7 +21685,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F382" t="n">
@@ -21905,7 +21905,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F386" t="n">
@@ -22063,7 +22063,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F389" t="n">
@@ -22121,7 +22121,7 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F390" t="n">
@@ -22179,7 +22179,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F391" t="n">
@@ -22287,7 +22287,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F393" t="n">
@@ -22461,7 +22461,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F396" t="n">
@@ -22573,7 +22573,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F398" t="n">
@@ -22631,7 +22631,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F399" t="n">
@@ -22855,7 +22855,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F403" t="n">
@@ -22909,7 +22909,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F404" t="n">
@@ -23461,7 +23461,7 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F414" t="n">
@@ -24063,7 +24063,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -24117,7 +24117,7 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F426" t="n">
@@ -24337,7 +24337,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F430" t="n">
@@ -24391,7 +24391,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F431" t="n">
@@ -24449,7 +24449,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F432" t="n">
@@ -24561,7 +24561,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F434" t="n">
@@ -24619,7 +24619,7 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F435" t="n">
@@ -24673,7 +24673,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F436" t="n">
@@ -24785,7 +24785,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F438" t="n">
@@ -24893,7 +24893,7 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F440" t="n">
@@ -24951,7 +24951,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F441" t="n">
@@ -25063,7 +25063,7 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F443" t="n">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F446" t="n">
@@ -25457,7 +25457,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F450" t="n">
@@ -25511,7 +25511,7 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F451" t="n">
@@ -25673,7 +25673,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F454" t="n">
@@ -26009,7 +26009,7 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F460" t="n">
@@ -26121,7 +26121,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F462" t="n">
@@ -26237,7 +26237,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F464" t="n">
@@ -26349,7 +26349,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F466" t="n">
@@ -26569,7 +26569,7 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F470" t="n">
@@ -26959,7 +26959,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F477" t="n">
@@ -27129,7 +27129,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F480" t="n">
@@ -27187,7 +27187,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F481" t="n">
@@ -27361,7 +27361,7 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F484" t="n">
@@ -27419,7 +27419,7 @@
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F485" t="n">
@@ -27855,7 +27855,7 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F493" t="n">
@@ -28079,7 +28079,7 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F497" t="n">
@@ -28133,7 +28133,7 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F498" t="n">
@@ -28191,7 +28191,7 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F499" t="n">
@@ -29037,7 +29037,7 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F514" t="n">
@@ -29319,7 +29319,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F519" t="n">
@@ -29481,7 +29481,7 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F522" t="n">
@@ -29593,7 +29593,7 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F524" t="n">
@@ -30431,7 +30431,7 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F539" t="n">
@@ -30547,7 +30547,7 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F541" t="n">
@@ -30717,7 +30717,7 @@
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F544" t="n">
@@ -30771,7 +30771,7 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F545" t="n">
@@ -31157,7 +31157,7 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F552" t="n">
@@ -31601,7 +31601,7 @@
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F560" t="n">
@@ -31659,7 +31659,7 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F561" t="n">
@@ -31941,7 +31941,7 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F566" t="n">
@@ -32277,7 +32277,7 @@
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F572" t="n">
@@ -32439,7 +32439,7 @@
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F575" t="n">
@@ -32555,7 +32555,7 @@
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F577" t="n">
@@ -32945,7 +32945,7 @@
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F584" t="n">
@@ -32999,7 +32999,7 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F585" t="n">
@@ -33107,7 +33107,7 @@
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F587" t="n">
@@ -33223,7 +33223,7 @@
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F589" t="n">
@@ -33281,7 +33281,7 @@
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F590" t="n">
@@ -33339,7 +33339,7 @@
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F591" t="n">
@@ -33509,7 +33509,7 @@
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F594" t="n">
@@ -33791,7 +33791,7 @@
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F599" t="n">
@@ -33903,7 +33903,7 @@
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F601" t="n">
@@ -34015,7 +34015,7 @@
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F603" t="n">
@@ -34131,7 +34131,7 @@
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F605" t="n">
@@ -34185,7 +34185,7 @@
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F606" t="n">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F607" t="n">
@@ -34301,7 +34301,7 @@
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F608" t="n">
@@ -34517,7 +34517,7 @@
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F612" t="n">
@@ -34749,7 +34749,7 @@
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F616" t="n">
@@ -34803,7 +34803,7 @@
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F617" t="n">
@@ -34969,7 +34969,7 @@
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F620" t="n">
@@ -35081,7 +35081,7 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F622" t="n">
@@ -35193,7 +35193,7 @@
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F624" t="n">
@@ -35243,7 +35243,7 @@
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F625" t="n">
@@ -35409,7 +35409,7 @@
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F628" t="n">
@@ -35525,7 +35525,7 @@
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F630" t="n">
@@ -35687,7 +35687,7 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F633" t="n">
@@ -35799,7 +35799,7 @@
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F635" t="n">
@@ -36243,7 +36243,7 @@
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F643" t="n">
@@ -36467,7 +36467,7 @@
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F647" t="n">
@@ -36517,7 +36517,7 @@
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F648" t="n">
@@ -36803,7 +36803,7 @@
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F653" t="n">
@@ -37197,7 +37197,7 @@
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F660" t="n">
@@ -37255,7 +37255,7 @@
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F661" t="n">
@@ -37425,7 +37425,7 @@
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F664" t="n">
@@ -37479,7 +37479,7 @@
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F665" t="n">
@@ -37649,7 +37649,7 @@
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F668" t="n">
@@ -37707,7 +37707,7 @@
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F669" t="n">
@@ -37877,7 +37877,7 @@
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F672" t="n">
@@ -37931,7 +37931,7 @@
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F673" t="n">
@@ -38093,7 +38093,7 @@
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F676" t="n">
@@ -38201,7 +38201,7 @@
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F678" t="n">
@@ -38637,7 +38637,7 @@
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F686" t="n">
@@ -38969,7 +38969,7 @@
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F692" t="n">
@@ -39027,7 +39027,7 @@
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F693" t="n">
@@ -39529,7 +39529,7 @@
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F702" t="n">
@@ -39699,7 +39699,7 @@
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F705" t="n">
@@ -39757,7 +39757,7 @@
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F706" t="n">
@@ -39927,7 +39927,7 @@
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F709" t="n">
@@ -41097,7 +41097,7 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F730" t="n">
@@ -41155,7 +41155,7 @@
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F731" t="n">
@@ -41495,7 +41495,7 @@
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F737" t="n">
@@ -41719,7 +41719,7 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F741" t="n">
@@ -41943,7 +41943,7 @@
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F745" t="n">
@@ -42001,7 +42001,7 @@
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F746" t="n">
@@ -42055,7 +42055,7 @@
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F747" t="n">
@@ -42333,7 +42333,7 @@
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F752" t="n">
@@ -42449,7 +42449,7 @@
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F754" t="n">
@@ -42561,7 +42561,7 @@
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F756" t="n">
@@ -42943,7 +42943,7 @@
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F763" t="n">
@@ -43221,7 +43221,7 @@
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F768" t="n">
@@ -43329,7 +43329,7 @@
       </c>
       <c r="E770" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F770" t="n">
@@ -43939,7 +43939,7 @@
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F781" t="n">
@@ -44279,7 +44279,7 @@
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F787" t="n">
@@ -44557,7 +44557,7 @@
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F792" t="n">
@@ -44665,7 +44665,7 @@
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F794" t="n">
@@ -44715,7 +44715,7 @@
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F795" t="n">
@@ -44773,7 +44773,7 @@
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F796" t="n">
@@ -44827,7 +44827,7 @@
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F797" t="n">
@@ -44935,7 +44935,7 @@
       </c>
       <c r="E799" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F799" t="n">
@@ -45205,7 +45205,7 @@
       </c>
       <c r="E804" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F804" t="n">
@@ -45649,7 +45649,7 @@
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F812" t="n">
@@ -45823,7 +45823,7 @@
       </c>
       <c r="E815" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F815" t="n">
@@ -45997,7 +45997,7 @@
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F818" t="n">
@@ -46333,7 +46333,7 @@
       </c>
       <c r="E824" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F824" t="n">
@@ -46449,7 +46449,7 @@
       </c>
       <c r="E826" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F826" t="n">
@@ -46619,7 +46619,7 @@
       </c>
       <c r="E829" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F829" t="n">
@@ -46727,7 +46727,7 @@
       </c>
       <c r="E831" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F831" t="n">
@@ -46781,7 +46781,7 @@
       </c>
       <c r="E832" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F832" t="n">
@@ -46893,7 +46893,7 @@
       </c>
       <c r="E834" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F834" t="n">
@@ -47171,7 +47171,7 @@
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F839" t="n">
@@ -47337,7 +47337,7 @@
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F842" t="n">
@@ -47449,7 +47449,7 @@
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F844" t="n">
@@ -47503,7 +47503,7 @@
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F845" t="n">
@@ -47557,7 +47557,7 @@
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F846" t="n">
@@ -47611,7 +47611,7 @@
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F847" t="n">
@@ -48263,7 +48263,7 @@
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F859" t="n">
@@ -48483,7 +48483,7 @@
       </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F863" t="n">
@@ -48595,7 +48595,7 @@
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F865" t="n">
@@ -48649,7 +48649,7 @@
       </c>
       <c r="E866" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F866" t="n">
@@ -48703,7 +48703,7 @@
       </c>
       <c r="E867" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F867" t="n">
@@ -48815,7 +48815,7 @@
       </c>
       <c r="E869" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F869" t="n">
@@ -48869,7 +48869,7 @@
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F870" t="n">
@@ -48919,7 +48919,7 @@
       </c>
       <c r="E871" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F871" t="n">
@@ -48977,7 +48977,7 @@
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F872" t="n">
@@ -49089,7 +49089,7 @@
       </c>
       <c r="E874" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F874" t="n">
@@ -49147,7 +49147,7 @@
       </c>
       <c r="E875" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F875" t="n">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F876" t="n">
@@ -49745,7 +49745,7 @@
       </c>
       <c r="E886" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F886" t="n">
@@ -49861,7 +49861,7 @@
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F888" t="n">
@@ -49915,7 +49915,7 @@
       </c>
       <c r="E889" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F889" t="n">
@@ -50077,7 +50077,7 @@
       </c>
       <c r="E892" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F892" t="n">
@@ -50463,7 +50463,7 @@
       </c>
       <c r="E899" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F899" t="n">
@@ -50517,7 +50517,7 @@
       </c>
       <c r="E900" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F900" t="n">
@@ -50567,7 +50567,7 @@
       </c>
       <c r="E901" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F901" t="n">
@@ -51215,7 +51215,7 @@
       </c>
       <c r="E913" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F913" t="n">
@@ -51327,7 +51327,7 @@
       </c>
       <c r="E915" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F915" t="n">
@@ -51381,7 +51381,7 @@
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F916" t="n">
@@ -51609,7 +51609,7 @@
       </c>
       <c r="E920" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F920" t="n">
@@ -51667,7 +51667,7 @@
       </c>
       <c r="E921" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F921" t="n">
@@ -51725,7 +51725,7 @@
       </c>
       <c r="E922" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F922" t="n">
@@ -51949,7 +51949,7 @@
       </c>
       <c r="E926" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F926" t="n">
@@ -52065,7 +52065,7 @@
       </c>
       <c r="E928" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F928" t="n">
@@ -52289,7 +52289,7 @@
       </c>
       <c r="E932" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F932" t="n">
@@ -52957,7 +52957,7 @@
       </c>
       <c r="E944" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F944" t="n">
@@ -53061,7 +53061,7 @@
       </c>
       <c r="E946" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F946" t="n">
@@ -53177,7 +53177,7 @@
       </c>
       <c r="E948" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F948" t="n">
@@ -53285,7 +53285,7 @@
       </c>
       <c r="E950" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F950" t="n">
@@ -53393,7 +53393,7 @@
       </c>
       <c r="E952" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F952" t="n">
@@ -53451,7 +53451,7 @@
       </c>
       <c r="E953" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F953" t="n">
@@ -53567,7 +53567,7 @@
       </c>
       <c r="E955" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F955" t="n">
@@ -53907,7 +53907,7 @@
       </c>
       <c r="E961" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F961" t="n">
@@ -54181,7 +54181,7 @@
       </c>
       <c r="E966" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F966" t="n">
@@ -54513,7 +54513,7 @@
       </c>
       <c r="E972" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F972" t="n">
@@ -54683,7 +54683,7 @@
       </c>
       <c r="E975" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F975" t="n">
@@ -54911,7 +54911,7 @@
       </c>
       <c r="E979" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F979" t="n">
@@ -55077,7 +55077,7 @@
       </c>
       <c r="E982" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F982" t="n">
@@ -55135,7 +55135,7 @@
       </c>
       <c r="E983" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F983" t="n">
@@ -55305,7 +55305,7 @@
       </c>
       <c r="E986" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F986" t="n">
@@ -55359,7 +55359,7 @@
       </c>
       <c r="E987" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F987" t="n">
@@ -55417,7 +55417,7 @@
       </c>
       <c r="E988" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>bajo riesgo</t>
         </is>
       </c>
       <c r="F988" t="n">
@@ -55803,7 +55803,7 @@
       </c>
       <c r="E995" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F995" t="n">
@@ -55911,7 +55911,7 @@
       </c>
       <c r="E997" t="inlineStr">
         <is>
-          <t>medio riesgo</t>
+          <t>alto riesgo</t>
         </is>
       </c>
       <c r="F997" t="n">

--- a/data/raw/german_credit_processed.xlsx
+++ b/data/raw/german_credit_processed.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,62 +429,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Sex</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Age_group</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Housing</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Risk_per_purpose</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Credit amount</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Duration</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Financial_profile</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Saving accounts</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Checking account</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Job_type</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Duration_estimated</t>
         </is>
